--- a/data/Frequency_sweep.xlsx
+++ b/data/Frequency_sweep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/Nick Lab/Analysis/Rheometry/Frequency/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A2EAD5-749E-0449-9A7D-1A080C5D86ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118D3B8F-8C87-804A-A8C2-D112CFFC93DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="500" windowWidth="29640" windowHeight="20880" activeTab="5" xr2:uid="{23A9AD00-BD58-4C85-88D2-6F62574CD7E4}"/>
+    <workbookView xWindow="1520" yWindow="500" windowWidth="29640" windowHeight="20880" activeTab="7" xr2:uid="{23A9AD00-BD58-4C85-88D2-6F62574CD7E4}"/>
   </bookViews>
   <sheets>
     <sheet name="WT_24" sheetId="1" r:id="rId1"/>
@@ -61,52 +61,52 @@
     <t>MPa</t>
   </si>
   <si>
-    <t>WT Parafilm- average G'</t>
+    <t>WT average G'</t>
   </si>
   <si>
-    <t>WT Parafilm- average G''</t>
+    <t>WT average G''</t>
   </si>
   <si>
-    <t>WT Parafilm- SD G'</t>
+    <t>WT SD G'</t>
   </si>
   <si>
-    <t>WT Parafilm- SD G''</t>
+    <t>WT SD G''</t>
   </si>
   <si>
-    <t>Spore- Parafilm- average G'</t>
+    <t>Spore- average G'</t>
   </si>
   <si>
-    <t>Spore- Parafilm- average G''</t>
+    <t>Spore- average G''</t>
   </si>
   <si>
-    <t>Spore- Parafilm- SD G'</t>
+    <t>Spore- SD G'</t>
   </si>
   <si>
-    <t>Spore- Parafilm- SD G''</t>
+    <t>Spore- SD G''</t>
   </si>
   <si>
-    <t>PGA- Parafilm- average G'</t>
+    <t>PGA- average G'</t>
   </si>
   <si>
-    <t>PGA- Parafilm- average G''</t>
+    <t>PGA- average G''</t>
   </si>
   <si>
-    <t>PGA- Parafilm- SD G'</t>
+    <t>PGA- SD G'</t>
   </si>
   <si>
-    <t>PGA- Parafilm- SD G''</t>
+    <t>PGA- SD G''</t>
   </si>
   <si>
-    <t>EPS- Parafilm- average G'</t>
+    <t>EPS- average G'</t>
   </si>
   <si>
-    <t>EPS- Parafilm- average G''</t>
+    <t>EPS- average G''</t>
   </si>
   <si>
-    <t>EPS- Parafilm- SD G'</t>
+    <t>EPS- SD G'</t>
   </si>
   <si>
-    <t>EPS- Parafilm- SD G''</t>
+    <t>EPS- SD G''</t>
   </si>
 </sst>
 </file>
@@ -1120,19 +1120,19 @@
         <v>1.83203E-4</v>
       </c>
       <c r="L3" s="3">
-        <f>AVERAGE(C3,F3,I3)</f>
+        <f t="shared" ref="L3:L13" si="0">AVERAGE(C3,F3,I3)</f>
         <v>6.01284E-4</v>
       </c>
       <c r="M3" s="3">
-        <f>AVERAGE(D3,G3,J3)</f>
+        <f t="shared" ref="M3:M13" si="1">AVERAGE(D3,G3,J3)</f>
         <v>1.62285E-4</v>
       </c>
       <c r="O3">
-        <f>_xlfn.STDEV.P(C3,F3,I3)</f>
+        <f t="shared" ref="O3:O13" si="2">_xlfn.STDEV.P(C3,F3,I3)</f>
         <v>4.3850490996871011E-5</v>
       </c>
       <c r="P3">
-        <f>_xlfn.STDEV.P(D3,G3,J3)</f>
+        <f t="shared" ref="P3:P13" si="3">_xlfn.STDEV.P(D3,G3,J3)</f>
         <v>1.5717063423765479E-5</v>
       </c>
     </row>
@@ -1160,19 +1160,19 @@
         <v>1.6706100000000001E-4</v>
       </c>
       <c r="L4" s="3">
-        <f>AVERAGE(C4,F4,I4)</f>
+        <f t="shared" si="0"/>
         <v>6.4301833333333335E-4</v>
       </c>
       <c r="M4" s="3">
-        <f>AVERAGE(D4,G4,J4)</f>
+        <f t="shared" si="1"/>
         <v>1.5584733333333335E-4</v>
       </c>
       <c r="O4">
-        <f>_xlfn.STDEV.P(C4,F4,I4)</f>
+        <f t="shared" si="2"/>
         <v>4.4235644197361442E-5</v>
       </c>
       <c r="P4">
-        <f>_xlfn.STDEV.P(D4,G4,J4)</f>
+        <f t="shared" si="3"/>
         <v>9.6988721108292972E-6</v>
       </c>
     </row>
@@ -1200,19 +1200,19 @@
         <v>1.7337200000000001E-4</v>
       </c>
       <c r="L5" s="3">
-        <f>AVERAGE(C5,F5,I5)</f>
+        <f t="shared" si="0"/>
         <v>6.8937433333333324E-4</v>
       </c>
       <c r="M5" s="3">
-        <f>AVERAGE(D5,G5,J5)</f>
+        <f t="shared" si="1"/>
         <v>1.5850999999999997E-4</v>
       </c>
       <c r="O5">
-        <f>_xlfn.STDEV.P(C5,F5,I5)</f>
+        <f t="shared" si="2"/>
         <v>4.6883346306432646E-5</v>
       </c>
       <c r="P5">
-        <f>_xlfn.STDEV.P(D5,G5,J5)</f>
+        <f t="shared" si="3"/>
         <v>1.2038785431540291E-5</v>
       </c>
     </row>
@@ -1240,19 +1240,19 @@
         <v>1.72036E-4</v>
       </c>
       <c r="L6" s="3">
-        <f>AVERAGE(C6,F6,I6)</f>
+        <f t="shared" si="0"/>
         <v>7.3147366666666659E-4</v>
       </c>
       <c r="M6" s="3">
-        <f>AVERAGE(D6,G6,J6)</f>
+        <f t="shared" si="1"/>
         <v>1.5884299999999998E-4</v>
       </c>
       <c r="O6">
-        <f>_xlfn.STDEV.P(C6,F6,I6)</f>
+        <f t="shared" si="2"/>
         <v>4.7361784625253397E-5</v>
       </c>
       <c r="P6">
-        <f>_xlfn.STDEV.P(D6,G6,J6)</f>
+        <f t="shared" si="3"/>
         <v>1.1697129077968947E-5</v>
       </c>
     </row>
@@ -1280,19 +1280,19 @@
         <v>1.7147500000000001E-4</v>
       </c>
       <c r="L7" s="3">
-        <f>AVERAGE(C7,F7,I7)</f>
+        <f t="shared" si="0"/>
         <v>7.7434900000000002E-4</v>
       </c>
       <c r="M7" s="3">
-        <f>AVERAGE(D7,G7,J7)</f>
+        <f t="shared" si="1"/>
         <v>1.6129866666666668E-4</v>
       </c>
       <c r="O7">
-        <f>_xlfn.STDEV.P(C7,F7,I7)</f>
+        <f t="shared" si="2"/>
         <v>4.8956443682113981E-5</v>
       </c>
       <c r="P7">
-        <f>_xlfn.STDEV.P(D7,G7,J7)</f>
+        <f t="shared" si="3"/>
         <v>1.1301049400633365E-5</v>
       </c>
     </row>
@@ -1320,19 +1320,19 @@
         <v>1.8277199999999999E-4</v>
       </c>
       <c r="L8" s="3">
-        <f>AVERAGE(C8,F8,I8)</f>
+        <f t="shared" si="0"/>
         <v>8.1675466666666669E-4</v>
       </c>
       <c r="M8" s="3">
-        <f>AVERAGE(D8,G8,J8)</f>
+        <f t="shared" si="1"/>
         <v>1.6736766666666664E-4</v>
       </c>
       <c r="O8">
-        <f>_xlfn.STDEV.P(C8,F8,I8)</f>
+        <f t="shared" si="2"/>
         <v>5.0814527806742666E-5</v>
       </c>
       <c r="P8">
-        <f>_xlfn.STDEV.P(D8,G8,J8)</f>
+        <f t="shared" si="3"/>
         <v>1.3721231585474469E-5</v>
       </c>
     </row>
@@ -1360,19 +1360,19 @@
         <v>1.87061E-4</v>
       </c>
       <c r="L9" s="3">
-        <f>AVERAGE(C9,F9,I9)</f>
+        <f t="shared" si="0"/>
         <v>8.5930066666666666E-4</v>
       </c>
       <c r="M9" s="3">
-        <f>AVERAGE(D9,G9,J9)</f>
+        <f t="shared" si="1"/>
         <v>1.74628E-4</v>
       </c>
       <c r="O9">
-        <f>_xlfn.STDEV.P(C9,F9,I9)</f>
+        <f t="shared" si="2"/>
         <v>5.1430947209718891E-5</v>
       </c>
       <c r="P9">
-        <f>_xlfn.STDEV.P(D9,G9,J9)</f>
+        <f t="shared" si="3"/>
         <v>1.2264551058504619E-5</v>
       </c>
     </row>
@@ -1400,19 +1400,19 @@
         <v>2.00946E-4</v>
       </c>
       <c r="L10" s="3">
-        <f>AVERAGE(C10,F10,I10)</f>
+        <f t="shared" si="0"/>
         <v>9.0370200000000004E-4</v>
       </c>
       <c r="M10" s="3">
-        <f>AVERAGE(D10,G10,J10)</f>
+        <f t="shared" si="1"/>
         <v>1.8703866666666666E-4</v>
       </c>
       <c r="O10">
-        <f>_xlfn.STDEV.P(C10,F10,I10)</f>
+        <f t="shared" si="2"/>
         <v>5.2260282363059079E-5</v>
       </c>
       <c r="P10">
-        <f>_xlfn.STDEV.P(D10,G10,J10)</f>
+        <f t="shared" si="3"/>
         <v>1.2759370134227719E-5</v>
       </c>
     </row>
@@ -1440,19 +1440,19 @@
         <v>2.20433E-4</v>
       </c>
       <c r="L11" s="3">
-        <f>AVERAGE(C11,F11,I11)</f>
+        <f t="shared" si="0"/>
         <v>9.5126333333333342E-4</v>
       </c>
       <c r="M11" s="3">
-        <f>AVERAGE(D11,G11,J11)</f>
+        <f t="shared" si="1"/>
         <v>2.0333666666666667E-4</v>
       </c>
       <c r="O11">
-        <f>_xlfn.STDEV.P(C11,F11,I11)</f>
+        <f t="shared" si="2"/>
         <v>5.0639064191809706E-5</v>
       </c>
       <c r="P11">
-        <f>_xlfn.STDEV.P(D11,G11,J11)</f>
+        <f t="shared" si="3"/>
         <v>1.4847542250786452E-5</v>
       </c>
     </row>
@@ -1480,19 +1480,19 @@
         <v>2.40838E-4</v>
       </c>
       <c r="L12" s="3">
-        <f>AVERAGE(C12,F12,I12)</f>
+        <f t="shared" si="0"/>
         <v>1.008658E-3</v>
       </c>
       <c r="M12" s="3">
-        <f>AVERAGE(D12,G12,J12)</f>
+        <f t="shared" si="1"/>
         <v>2.2363466666666665E-4</v>
       </c>
       <c r="O12">
-        <f>_xlfn.STDEV.P(C12,F12,I12)</f>
+        <f t="shared" si="2"/>
         <v>4.4327269199293917E-5</v>
       </c>
       <c r="P12">
-        <f>_xlfn.STDEV.P(D12,G12,J12)</f>
+        <f t="shared" si="3"/>
         <v>1.4986790835784541E-5</v>
       </c>
     </row>
@@ -1520,19 +1520,19 @@
         <v>2.6867500000000001E-4</v>
       </c>
       <c r="L13" s="3">
-        <f>AVERAGE(C13,F13,I13)</f>
+        <f t="shared" si="0"/>
         <v>1.0709099999999998E-3</v>
       </c>
       <c r="M13" s="3">
-        <f>AVERAGE(D13,G13,J13)</f>
+        <f t="shared" si="1"/>
         <v>2.5361733333333336E-4</v>
       </c>
       <c r="O13">
-        <f>_xlfn.STDEV.P(C13,F13,I13)</f>
+        <f t="shared" si="2"/>
         <v>2.6733934739702348E-5</v>
       </c>
       <c r="P13">
-        <f>_xlfn.STDEV.P(D13,G13,J13)</f>
+        <f t="shared" si="3"/>
         <v>1.6118254957931673E-5</v>
       </c>
     </row>
@@ -2154,19 +2154,19 @@
         <v>1.40598E-4</v>
       </c>
       <c r="L3" s="3">
-        <f>AVERAGE(C3,F3,I3)</f>
+        <f t="shared" ref="L3:L13" si="0">AVERAGE(C3,F3,I3)</f>
         <v>6.8027733333333345E-4</v>
       </c>
       <c r="M3" s="3">
-        <f>AVERAGE(D3,G3,J3)</f>
+        <f t="shared" ref="M3:M13" si="1">AVERAGE(D3,G3,J3)</f>
         <v>1.1506406666666666E-4</v>
       </c>
       <c r="O3">
-        <f>_xlfn.STDEV.P(C3,F3,I3)</f>
+        <f t="shared" ref="O3:O13" si="2">_xlfn.STDEV.P(C3,F3,I3)</f>
         <v>6.5637570208599937E-5</v>
       </c>
       <c r="P3">
-        <f>_xlfn.STDEV.P(D3,G3,J3)</f>
+        <f t="shared" ref="P3:P13" si="3">_xlfn.STDEV.P(D3,G3,J3)</f>
         <v>1.8160183185811266E-5</v>
       </c>
     </row>
@@ -2193,19 +2193,19 @@
         <v>1.4214499999999999E-4</v>
       </c>
       <c r="L4" s="3">
-        <f>AVERAGE(C4,F4,I4)</f>
+        <f t="shared" si="0"/>
         <v>7.1045966666666673E-4</v>
       </c>
       <c r="M4" s="3">
-        <f>AVERAGE(D4,G4,J4)</f>
+        <f t="shared" si="1"/>
         <v>1.157727E-4</v>
       </c>
       <c r="O4">
-        <f>_xlfn.STDEV.P(C4,F4,I4)</f>
+        <f t="shared" si="2"/>
         <v>6.5570766948558926E-5</v>
       </c>
       <c r="P4">
-        <f>_xlfn.STDEV.P(D4,G4,J4)</f>
+        <f t="shared" si="3"/>
         <v>1.8878327886229748E-5</v>
       </c>
     </row>
@@ -2232,19 +2232,19 @@
         <v>1.41049E-4</v>
       </c>
       <c r="L5" s="3">
-        <f>AVERAGE(C5,F5,I5)</f>
+        <f t="shared" si="0"/>
         <v>7.3580733333333337E-4</v>
       </c>
       <c r="M5" s="3">
-        <f>AVERAGE(D5,G5,J5)</f>
+        <f t="shared" si="1"/>
         <v>1.1394649999999999E-4</v>
       </c>
       <c r="O5">
-        <f>_xlfn.STDEV.P(C5,F5,I5)</f>
+        <f t="shared" si="2"/>
         <v>6.6520177557055735E-5</v>
       </c>
       <c r="P5">
-        <f>_xlfn.STDEV.P(D5,G5,J5)</f>
+        <f t="shared" si="3"/>
         <v>1.9265766612483051E-5</v>
       </c>
     </row>
@@ -2271,19 +2271,19 @@
         <v>1.3635700000000001E-4</v>
       </c>
       <c r="L6" s="3">
-        <f>AVERAGE(C6,F6,I6)</f>
+        <f t="shared" si="0"/>
         <v>7.6023300000000002E-4</v>
       </c>
       <c r="M6" s="3">
-        <f>AVERAGE(D6,G6,J6)</f>
+        <f t="shared" si="1"/>
         <v>1.1517500000000001E-4</v>
       </c>
       <c r="O6">
-        <f>_xlfn.STDEV.P(C6,F6,I6)</f>
+        <f t="shared" si="2"/>
         <v>6.6323964100466746E-5</v>
       </c>
       <c r="P6">
-        <f>_xlfn.STDEV.P(D6,G6,J6)</f>
+        <f t="shared" si="3"/>
         <v>1.4977975096787954E-5</v>
       </c>
     </row>
@@ -2310,19 +2310,19 @@
         <v>1.44184E-4</v>
       </c>
       <c r="L7" s="3">
-        <f>AVERAGE(C7,F7,I7)</f>
+        <f t="shared" si="0"/>
         <v>7.873783333333333E-4</v>
       </c>
       <c r="M7" s="3">
-        <f>AVERAGE(D7,G7,J7)</f>
+        <f t="shared" si="1"/>
         <v>1.1933133333333333E-4</v>
       </c>
       <c r="O7">
-        <f>_xlfn.STDEV.P(C7,F7,I7)</f>
+        <f t="shared" si="2"/>
         <v>6.847551029544957E-5</v>
       </c>
       <c r="P7">
-        <f>_xlfn.STDEV.P(D7,G7,J7)</f>
+        <f t="shared" si="3"/>
         <v>1.7583649684357972E-5</v>
       </c>
     </row>
@@ -2349,19 +2349,19 @@
         <v>1.5155600000000001E-4</v>
       </c>
       <c r="L8" s="3">
-        <f>AVERAGE(C8,F8,I8)</f>
+        <f t="shared" si="0"/>
         <v>8.1346933333333331E-4</v>
       </c>
       <c r="M8" s="3">
-        <f>AVERAGE(D8,G8,J8)</f>
+        <f t="shared" si="1"/>
         <v>1.2598233333333334E-4</v>
       </c>
       <c r="O8">
-        <f>_xlfn.STDEV.P(C8,F8,I8)</f>
+        <f t="shared" si="2"/>
         <v>7.1517605526347298E-5</v>
       </c>
       <c r="P8">
-        <f>_xlfn.STDEV.P(D8,G8,J8)</f>
+        <f t="shared" si="3"/>
         <v>1.864832682992112E-5</v>
       </c>
     </row>
@@ -2388,19 +2388,19 @@
         <v>1.5330699999999999E-4</v>
       </c>
       <c r="L9" s="3">
-        <f>AVERAGE(C9,F9,I9)</f>
+        <f t="shared" si="0"/>
         <v>8.4143666666666673E-4</v>
       </c>
       <c r="M9" s="3">
-        <f>AVERAGE(D9,G9,J9)</f>
+        <f t="shared" si="1"/>
         <v>1.3402099999999998E-4</v>
       </c>
       <c r="O9">
-        <f>_xlfn.STDEV.P(C9,F9,I9)</f>
+        <f t="shared" si="2"/>
         <v>7.1603432684629173E-5</v>
       </c>
       <c r="P9">
-        <f>_xlfn.STDEV.P(D9,G9,J9)</f>
+        <f t="shared" si="3"/>
         <v>1.3761977643735169E-5</v>
       </c>
     </row>
@@ -2427,19 +2427,19 @@
         <v>1.64792E-4</v>
       </c>
       <c r="L10" s="3">
-        <f>AVERAGE(C10,F10,I10)</f>
+        <f t="shared" si="0"/>
         <v>8.7296900000000002E-4</v>
       </c>
       <c r="M10" s="3">
-        <f>AVERAGE(D10,G10,J10)</f>
+        <f t="shared" si="1"/>
         <v>1.4534333333333333E-4</v>
       </c>
       <c r="O10">
-        <f>_xlfn.STDEV.P(C10,F10,I10)</f>
+        <f t="shared" si="2"/>
         <v>7.4444123237947212E-5</v>
       </c>
       <c r="P10">
-        <f>_xlfn.STDEV.P(D10,G10,J10)</f>
+        <f t="shared" si="3"/>
         <v>1.5329961781499079E-5</v>
       </c>
     </row>
@@ -2466,19 +2466,19 @@
         <v>1.7732499999999999E-4</v>
       </c>
       <c r="L11" s="3">
-        <f>AVERAGE(C11,F11,I11)</f>
+        <f t="shared" si="0"/>
         <v>9.0638533333333349E-4</v>
       </c>
       <c r="M11" s="3">
-        <f>AVERAGE(D11,G11,J11)</f>
+        <f t="shared" si="1"/>
         <v>1.5414499999999998E-4</v>
       </c>
       <c r="O11">
-        <f>_xlfn.STDEV.P(C11,F11,I11)</f>
+        <f t="shared" si="2"/>
         <v>7.7393810076919074E-5</v>
       </c>
       <c r="P11">
-        <f>_xlfn.STDEV.P(D11,G11,J11)</f>
+        <f t="shared" si="3"/>
         <v>1.7850215012710622E-5</v>
       </c>
     </row>
@@ -2505,19 +2505,19 @@
         <v>1.8325899999999999E-4</v>
       </c>
       <c r="L12" s="3">
-        <f>AVERAGE(C12,F12,I12)</f>
+        <f t="shared" si="0"/>
         <v>9.5094433333333327E-4</v>
       </c>
       <c r="M12" s="3">
-        <f>AVERAGE(D12,G12,J12)</f>
+        <f t="shared" si="1"/>
         <v>1.6385666666666665E-4</v>
       </c>
       <c r="O12">
-        <f>_xlfn.STDEV.P(C12,F12,I12)</f>
+        <f t="shared" si="2"/>
         <v>8.2112331011987584E-5</v>
       </c>
       <c r="P12">
-        <f>_xlfn.STDEV.P(D12,G12,J12)</f>
+        <f t="shared" si="3"/>
         <v>1.6030639087558404E-5</v>
       </c>
     </row>
@@ -2544,19 +2544,19 @@
         <v>2.0433300000000001E-4</v>
       </c>
       <c r="L13" s="3">
-        <f>AVERAGE(C13,F13,I13)</f>
+        <f t="shared" si="0"/>
         <v>1.0026563333333334E-3</v>
       </c>
       <c r="M13" s="3">
-        <f>AVERAGE(D13,G13,J13)</f>
+        <f t="shared" si="1"/>
         <v>1.7999499999999999E-4</v>
       </c>
       <c r="O13">
-        <f>_xlfn.STDEV.P(C13,F13,I13)</f>
+        <f t="shared" si="2"/>
         <v>9.4027833114574289E-5</v>
       </c>
       <c r="P13">
-        <f>_xlfn.STDEV.P(D13,G13,J13)</f>
+        <f t="shared" si="3"/>
         <v>1.8627962976843892E-5</v>
       </c>
     </row>
@@ -3178,19 +3178,19 @@
         <v>1.4660199999999999E-4</v>
       </c>
       <c r="L3" s="3">
-        <f>AVERAGE(C3,F3,I3)</f>
+        <f t="shared" ref="L3:L13" si="0">AVERAGE(C3,F3,I3)</f>
         <v>6.111333333333333E-4</v>
       </c>
       <c r="M3" s="3">
-        <f>AVERAGE(D3,G3,J3)</f>
+        <f t="shared" ref="M3:M13" si="1">AVERAGE(D3,G3,J3)</f>
         <v>1.4932533333333333E-4</v>
       </c>
       <c r="O3">
-        <f>_xlfn.STDEV.P(C3,F3,I3)</f>
+        <f t="shared" ref="O3:O13" si="2">_xlfn.STDEV.P(C3,F3,I3)</f>
         <v>1.3725603358525082E-5</v>
       </c>
       <c r="P3">
-        <f>_xlfn.STDEV.P(D3,G3,J3)</f>
+        <f t="shared" ref="P3:P13" si="3">_xlfn.STDEV.P(D3,G3,J3)</f>
         <v>4.8045318421488546E-6</v>
       </c>
     </row>
@@ -3217,19 +3217,19 @@
         <v>1.4673400000000001E-4</v>
       </c>
       <c r="L4" s="3">
-        <f>AVERAGE(C4,F4,I4)</f>
+        <f t="shared" si="0"/>
         <v>6.5628633333333333E-4</v>
       </c>
       <c r="M4" s="3">
-        <f>AVERAGE(D4,G4,J4)</f>
+        <f t="shared" si="1"/>
         <v>1.4773966666666667E-4</v>
       </c>
       <c r="O4">
-        <f>_xlfn.STDEV.P(C4,F4,I4)</f>
+        <f t="shared" si="2"/>
         <v>1.3428380501344494E-5</v>
       </c>
       <c r="P4">
-        <f>_xlfn.STDEV.P(D4,G4,J4)</f>
+        <f t="shared" si="3"/>
         <v>4.9814326141070042E-6</v>
       </c>
     </row>
@@ -3256,19 +3256,19 @@
         <v>1.43769E-4</v>
       </c>
       <c r="L5" s="3">
-        <f>AVERAGE(C5,F5,I5)</f>
+        <f t="shared" si="0"/>
         <v>7.01226E-4</v>
       </c>
       <c r="M5" s="3">
-        <f>AVERAGE(D5,G5,J5)</f>
+        <f t="shared" si="1"/>
         <v>1.4714599999999999E-4</v>
       </c>
       <c r="O5">
-        <f>_xlfn.STDEV.P(C5,F5,I5)</f>
+        <f t="shared" si="2"/>
         <v>1.3382489977578906E-5</v>
       </c>
       <c r="P5">
-        <f>_xlfn.STDEV.P(D5,G5,J5)</f>
+        <f t="shared" si="3"/>
         <v>5.7501500849977822E-6</v>
       </c>
     </row>
@@ -3295,19 +3295,19 @@
         <v>1.44962E-4</v>
       </c>
       <c r="L6" s="3">
-        <f>AVERAGE(C6,F6,I6)</f>
+        <f t="shared" si="0"/>
         <v>7.4393566666666657E-4</v>
       </c>
       <c r="M6" s="3">
-        <f>AVERAGE(D6,G6,J6)</f>
+        <f t="shared" si="1"/>
         <v>1.4782666666666666E-4</v>
       </c>
       <c r="O6">
-        <f>_xlfn.STDEV.P(C6,F6,I6)</f>
+        <f t="shared" si="2"/>
         <v>1.3047240559682416E-5</v>
       </c>
       <c r="P6">
-        <f>_xlfn.STDEV.P(D6,G6,J6)</f>
+        <f t="shared" si="3"/>
         <v>5.9385354722823253E-6</v>
       </c>
     </row>
@@ -3334,19 +3334,19 @@
         <v>1.4565300000000001E-4</v>
       </c>
       <c r="L7" s="3">
-        <f>AVERAGE(C7,F7,I7)</f>
+        <f t="shared" si="0"/>
         <v>7.8747266666666675E-4</v>
       </c>
       <c r="M7" s="3">
-        <f>AVERAGE(D7,G7,J7)</f>
+        <f t="shared" si="1"/>
         <v>1.4830266666666667E-4</v>
       </c>
       <c r="O7">
-        <f>_xlfn.STDEV.P(C7,F7,I7)</f>
+        <f t="shared" si="2"/>
         <v>1.338545554780344E-5</v>
       </c>
       <c r="P7">
-        <f>_xlfn.STDEV.P(D7,G7,J7)</f>
+        <f t="shared" si="3"/>
         <v>5.0727278876578996E-6</v>
       </c>
     </row>
@@ -3373,19 +3373,19 @@
         <v>1.47412E-4</v>
       </c>
       <c r="L8" s="3">
-        <f>AVERAGE(C8,F8,I8)</f>
+        <f t="shared" si="0"/>
         <v>8.2988533333333331E-4</v>
       </c>
       <c r="M8" s="3">
-        <f>AVERAGE(D8,G8,J8)</f>
+        <f t="shared" si="1"/>
         <v>1.5132099999999997E-4</v>
       </c>
       <c r="O8">
-        <f>_xlfn.STDEV.P(C8,F8,I8)</f>
+        <f t="shared" si="2"/>
         <v>1.3594510272737178E-5</v>
       </c>
       <c r="P8">
-        <f>_xlfn.STDEV.P(D8,G8,J8)</f>
+        <f t="shared" si="3"/>
         <v>6.8980939879554129E-6</v>
       </c>
     </row>
@@ -3412,19 +3412,19 @@
         <v>1.5177100000000001E-4</v>
       </c>
       <c r="L9" s="3">
-        <f>AVERAGE(C9,F9,I9)</f>
+        <f t="shared" si="0"/>
         <v>8.7154766666666661E-4</v>
       </c>
       <c r="M9" s="3">
-        <f>AVERAGE(D9,G9,J9)</f>
+        <f t="shared" si="1"/>
         <v>1.5548299999999999E-4</v>
       </c>
       <c r="O9">
-        <f>_xlfn.STDEV.P(C9,F9,I9)</f>
+        <f t="shared" si="2"/>
         <v>1.3464964620162335E-5</v>
       </c>
       <c r="P9">
-        <f>_xlfn.STDEV.P(D9,G9,J9)</f>
+        <f t="shared" si="3"/>
         <v>7.0631045581953563E-6</v>
       </c>
     </row>
@@ -3451,19 +3451,19 @@
         <v>1.5960799999999999E-4</v>
       </c>
       <c r="L10" s="3">
-        <f>AVERAGE(C10,F10,I10)</f>
+        <f t="shared" si="0"/>
         <v>9.1445466666666662E-4</v>
       </c>
       <c r="M10" s="3">
-        <f>AVERAGE(D10,G10,J10)</f>
+        <f t="shared" si="1"/>
         <v>1.6492500000000001E-4</v>
       </c>
       <c r="O10">
-        <f>_xlfn.STDEV.P(C10,F10,I10)</f>
+        <f t="shared" si="2"/>
         <v>1.4152719039895549E-5</v>
       </c>
       <c r="P10">
-        <f>_xlfn.STDEV.P(D10,G10,J10)</f>
+        <f t="shared" si="3"/>
         <v>9.9029452521291174E-6</v>
       </c>
     </row>
@@ -3490,19 +3490,19 @@
         <v>1.72053E-4</v>
       </c>
       <c r="L11" s="3">
-        <f>AVERAGE(C11,F11,I11)</f>
+        <f t="shared" si="0"/>
         <v>9.5899233333333336E-4</v>
       </c>
       <c r="M11" s="3">
-        <f>AVERAGE(D11,G11,J11)</f>
+        <f t="shared" si="1"/>
         <v>1.7959566666666667E-4</v>
       </c>
       <c r="O11">
-        <f>_xlfn.STDEV.P(C11,F11,I11)</f>
+        <f t="shared" si="2"/>
         <v>1.516805707912373E-5</v>
       </c>
       <c r="P11">
-        <f>_xlfn.STDEV.P(D11,G11,J11)</f>
+        <f t="shared" si="3"/>
         <v>1.3698274205980191E-5</v>
       </c>
     </row>
@@ -3529,19 +3529,19 @@
         <v>1.9108499999999999E-4</v>
       </c>
       <c r="L12" s="3">
-        <f>AVERAGE(C12,F12,I12)</f>
+        <f t="shared" si="0"/>
         <v>1.0111536666666668E-3</v>
       </c>
       <c r="M12" s="3">
-        <f>AVERAGE(D12,G12,J12)</f>
+        <f t="shared" si="1"/>
         <v>1.9921133333333332E-4</v>
       </c>
       <c r="O12">
-        <f>_xlfn.STDEV.P(C12,F12,I12)</f>
+        <f t="shared" si="2"/>
         <v>1.7835841636684521E-5</v>
       </c>
       <c r="P12">
-        <f>_xlfn.STDEV.P(D12,G12,J12)</f>
+        <f t="shared" si="3"/>
         <v>1.5469403357021307E-5</v>
       </c>
     </row>
@@ -3568,19 +3568,19 @@
         <v>2.1804999999999999E-4</v>
       </c>
       <c r="L13" s="3">
-        <f>AVERAGE(C13,F13,I13)</f>
+        <f t="shared" si="0"/>
         <v>1.0613533333333333E-3</v>
       </c>
       <c r="M13" s="3">
-        <f>AVERAGE(D13,G13,J13)</f>
+        <f t="shared" si="1"/>
         <v>2.2463666666666668E-4</v>
       </c>
       <c r="O13">
-        <f>_xlfn.STDEV.P(C13,F13,I13)</f>
+        <f t="shared" si="2"/>
         <v>2.4737138521304867E-5</v>
       </c>
       <c r="P13">
-        <f>_xlfn.STDEV.P(D13,G13,J13)</f>
+        <f t="shared" si="3"/>
         <v>1.4604618957332946E-5</v>
       </c>
     </row>
@@ -4202,19 +4202,19 @@
         <v>1.51519E-4</v>
       </c>
       <c r="L3" s="3">
-        <f>AVERAGE(C3,F3,I3)</f>
+        <f t="shared" ref="L3:L13" si="0">AVERAGE(C3,F3,I3)</f>
         <v>5.613156666666667E-4</v>
       </c>
       <c r="M3" s="3">
-        <f>AVERAGE(D3,G3,J3)</f>
+        <f t="shared" ref="M3:M13" si="1">AVERAGE(D3,G3,J3)</f>
         <v>1.7401266666666664E-4</v>
       </c>
       <c r="O3">
-        <f>_xlfn.STDEV.P(C3,F3,I3)</f>
+        <f t="shared" ref="O3:O13" si="2">_xlfn.STDEV.P(C3,F3,I3)</f>
         <v>4.3519670903575731E-6</v>
       </c>
       <c r="P3">
-        <f>_xlfn.STDEV.P(D3,G3,J3)</f>
+        <f t="shared" ref="P3:P13" si="3">_xlfn.STDEV.P(D3,G3,J3)</f>
         <v>1.653378662685055E-5</v>
       </c>
     </row>
@@ -4241,19 +4241,19 @@
         <v>1.5384E-4</v>
       </c>
       <c r="L4" s="3">
-        <f>AVERAGE(C4,F4,I4)</f>
+        <f t="shared" si="0"/>
         <v>6.0241133333333334E-4</v>
       </c>
       <c r="M4" s="3">
-        <f>AVERAGE(D4,G4,J4)</f>
+        <f t="shared" si="1"/>
         <v>1.7522166666666668E-4</v>
       </c>
       <c r="O4">
-        <f>_xlfn.STDEV.P(C4,F4,I4)</f>
+        <f t="shared" si="2"/>
         <v>4.9813046706884373E-6</v>
       </c>
       <c r="P4">
-        <f>_xlfn.STDEV.P(D4,G4,J4)</f>
+        <f t="shared" si="3"/>
         <v>1.5612191995004702E-5</v>
       </c>
     </row>
@@ -4280,19 +4280,19 @@
         <v>1.54301E-4</v>
       </c>
       <c r="L5" s="3">
-        <f>AVERAGE(C5,F5,I5)</f>
+        <f t="shared" si="0"/>
         <v>6.4937633333333339E-4</v>
       </c>
       <c r="M5" s="3">
-        <f>AVERAGE(D5,G5,J5)</f>
+        <f t="shared" si="1"/>
         <v>1.7462333333333332E-4</v>
       </c>
       <c r="O5">
-        <f>_xlfn.STDEV.P(C5,F5,I5)</f>
+        <f t="shared" si="2"/>
         <v>8.5960437540895496E-6</v>
       </c>
       <c r="P5">
-        <f>_xlfn.STDEV.P(D5,G5,J5)</f>
+        <f t="shared" si="3"/>
         <v>1.4837521678351659E-5</v>
       </c>
     </row>
@@ -4319,19 +4319,19 @@
         <v>1.5726100000000001E-4</v>
       </c>
       <c r="L6" s="3">
-        <f>AVERAGE(C6,F6,I6)</f>
+        <f t="shared" si="0"/>
         <v>6.8721900000000009E-4</v>
       </c>
       <c r="M6" s="3">
-        <f>AVERAGE(D6,G6,J6)</f>
+        <f t="shared" si="1"/>
         <v>1.79075E-4</v>
       </c>
       <c r="O6">
-        <f>_xlfn.STDEV.P(C6,F6,I6)</f>
+        <f t="shared" si="2"/>
         <v>5.8026359527373575E-6</v>
       </c>
       <c r="P6">
-        <f>_xlfn.STDEV.P(D6,G6,J6)</f>
+        <f t="shared" si="3"/>
         <v>1.5615937072960638E-5</v>
       </c>
     </row>
@@ -4358,19 +4358,19 @@
         <v>1.62447E-4</v>
       </c>
       <c r="L7" s="3">
-        <f>AVERAGE(C7,F7,I7)</f>
+        <f t="shared" si="0"/>
         <v>7.3095166666666672E-4</v>
       </c>
       <c r="M7" s="3">
-        <f>AVERAGE(D7,G7,J7)</f>
+        <f t="shared" si="1"/>
         <v>1.8441933333333336E-4</v>
       </c>
       <c r="O7">
-        <f>_xlfn.STDEV.P(C7,F7,I7)</f>
+        <f t="shared" si="2"/>
         <v>5.5751494050732698E-6</v>
       </c>
       <c r="P7">
-        <f>_xlfn.STDEV.P(D7,G7,J7)</f>
+        <f t="shared" si="3"/>
         <v>1.5945173696834487E-5</v>
       </c>
     </row>
@@ -4397,19 +4397,19 @@
         <v>1.71373E-4</v>
       </c>
       <c r="L8" s="3">
-        <f>AVERAGE(C8,F8,I8)</f>
+        <f t="shared" si="0"/>
         <v>7.7198633333333327E-4</v>
       </c>
       <c r="M8" s="3">
-        <f>AVERAGE(D8,G8,J8)</f>
+        <f t="shared" si="1"/>
         <v>1.9210199999999998E-4</v>
       </c>
       <c r="O8">
-        <f>_xlfn.STDEV.P(C8,F8,I8)</f>
+        <f t="shared" si="2"/>
         <v>6.9002919906012221E-6</v>
       </c>
       <c r="P8">
-        <f>_xlfn.STDEV.P(D8,G8,J8)</f>
+        <f t="shared" si="3"/>
         <v>1.5048699412241577E-5</v>
       </c>
     </row>
@@ -4436,19 +4436,19 @@
         <v>1.8111000000000001E-4</v>
       </c>
       <c r="L9" s="3">
-        <f>AVERAGE(C9,F9,I9)</f>
+        <f t="shared" si="0"/>
         <v>8.1516833333333339E-4</v>
       </c>
       <c r="M9" s="3">
-        <f>AVERAGE(D9,G9,J9)</f>
+        <f t="shared" si="1"/>
         <v>2.0196700000000003E-4</v>
       </c>
       <c r="O9">
-        <f>_xlfn.STDEV.P(C9,F9,I9)</f>
+        <f t="shared" si="2"/>
         <v>7.179690166635939E-6</v>
       </c>
       <c r="P9">
-        <f>_xlfn.STDEV.P(D9,G9,J9)</f>
+        <f t="shared" si="3"/>
         <v>1.5448535917684879E-5</v>
       </c>
     </row>
@@ -4475,19 +4475,19 @@
         <v>1.94413E-4</v>
       </c>
       <c r="L10" s="3">
-        <f>AVERAGE(C10,F10,I10)</f>
+        <f t="shared" si="0"/>
         <v>8.6007033333333326E-4</v>
       </c>
       <c r="M10" s="3">
-        <f>AVERAGE(D10,G10,J10)</f>
+        <f t="shared" si="1"/>
         <v>2.1589999999999999E-4</v>
       </c>
       <c r="O10">
-        <f>_xlfn.STDEV.P(C10,F10,I10)</f>
+        <f t="shared" si="2"/>
         <v>8.3295854371964585E-6</v>
       </c>
       <c r="P10">
-        <f>_xlfn.STDEV.P(D10,G10,J10)</f>
+        <f t="shared" si="3"/>
         <v>1.5889348570662046E-5</v>
       </c>
     </row>
@@ -4514,19 +4514,19 @@
         <v>2.15453E-4</v>
       </c>
       <c r="L11" s="3">
-        <f>AVERAGE(C11,F11,I11)</f>
+        <f t="shared" si="0"/>
         <v>9.1120366666666661E-4</v>
       </c>
       <c r="M11" s="3">
-        <f>AVERAGE(D11,G11,J11)</f>
+        <f t="shared" si="1"/>
         <v>2.3693200000000003E-4</v>
       </c>
       <c r="O11">
-        <f>_xlfn.STDEV.P(C11,F11,I11)</f>
+        <f t="shared" si="2"/>
         <v>9.1892739406089898E-6</v>
       </c>
       <c r="P11">
-        <f>_xlfn.STDEV.P(D11,G11,J11)</f>
+        <f t="shared" si="3"/>
         <v>1.6051568209991207E-5</v>
       </c>
     </row>
@@ -4553,19 +4553,19 @@
         <v>2.38395E-4</v>
       </c>
       <c r="L12" s="3">
-        <f>AVERAGE(C12,F12,I12)</f>
+        <f t="shared" si="0"/>
         <v>9.7460499999999992E-4</v>
       </c>
       <c r="M12" s="3">
-        <f>AVERAGE(D12,G12,J12)</f>
+        <f t="shared" si="1"/>
         <v>2.6162666666666663E-4</v>
       </c>
       <c r="O12">
-        <f>_xlfn.STDEV.P(C12,F12,I12)</f>
+        <f t="shared" si="2"/>
         <v>1.0427717423610335E-5</v>
       </c>
       <c r="P12">
-        <f>_xlfn.STDEV.P(D12,G12,J12)</f>
+        <f t="shared" si="3"/>
         <v>1.7128152504640487E-5</v>
       </c>
     </row>
@@ -4592,19 +4592,19 @@
         <v>2.7415000000000002E-4</v>
       </c>
       <c r="L13" s="3">
-        <f>AVERAGE(C13,F13,I13)</f>
+        <f t="shared" si="0"/>
         <v>1.0521666666666667E-3</v>
       </c>
       <c r="M13" s="3">
-        <f>AVERAGE(D13,G13,J13)</f>
+        <f t="shared" si="1"/>
         <v>2.9721100000000002E-4</v>
       </c>
       <c r="O13">
-        <f>_xlfn.STDEV.P(C13,F13,I13)</f>
+        <f t="shared" si="2"/>
         <v>1.5404580126991127E-5</v>
       </c>
       <c r="P13">
-        <f>_xlfn.STDEV.P(D13,G13,J13)</f>
+        <f t="shared" si="3"/>
         <v>1.7737287410048539E-5</v>
       </c>
     </row>
